--- a/htr-FHIR/ig/mappingInformateurCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingInformateurCDAFHIR.xlsx
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T15:29:00+00:00</t>
+    <t>2025-03-12T13:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingInformateurCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingInformateurCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="41">
   <si>
     <t>Property</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-14T15:47:10+00:00</t>
+    <t>2025-03-25T13:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
   <si>
     <t>Ce ConceptMap présente deux groupes de mapping : 
  - Groupe Mapping 1 : entre le modèle métier de l'informateur et l'élément CDA informant
- - Groupe Mapping 2 : entre l'élément CDA informant et InformantExtension en FHIR</t>
+ - Groupe Mapping 2 : entre l'élément CDA informant et l'extension FHIR InformantExtension</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -96,24 +96,24 @@
     <t>Source</t>
   </si>
   <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Relationship</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/Informateur</t>
   </si>
   <si>
-    <t>Target</t>
+    <t/>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-informant</t>
   </si>
   <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Relationship</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>Informateur</t>
   </si>
   <si>
@@ -132,7 +132,7 @@
     <t>informant.relatedEntity</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-informant-extension</t>
+    <t>http://hl7.org/fhir/uv/fhir-clinical-document/StructureDefinition/informant-extension</t>
   </si>
   <si>
     <t>extension:InformantExtension</t>
@@ -272,7 +272,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -386,22 +386,6 @@
         <v>24</v>
       </c>
       <c r="B14" s="2"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>28</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -418,33 +402,33 @@
         <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s" s="2">
         <v>31</v>
       </c>
-      <c r="C2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>28</v>
-      </c>
       <c r="E2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -501,33 +485,33 @@
         <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s" s="2">
         <v>38</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">

--- a/htr-FHIR/ig/mappingInformateurCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingInformateurCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T13:52:25+00:00</t>
+    <t>2025-03-25T14:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingInformateurCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingInformateurCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T14:07:20+00:00</t>
+    <t>2025-03-31T09:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingInformateurCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingInformateurCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T09:17:15+00:00</t>
+    <t>2025-04-14T15:21:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingInformateurCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingInformateurCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-14T15:21:44+00:00</t>
+    <t>2025-04-23T09:31:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingInformateurCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingInformateurCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:31:53+00:00</t>
+    <t>2025-04-24T14:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingInformateurCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingInformateurCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T14:52:25+00:00</t>
+    <t>2025-04-28T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingInformateurCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingInformateurCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:47:42+00:00</t>
+    <t>2025-04-28T07:48:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingInformateurCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingInformateurCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:48:19+00:00</t>
+    <t>2025-04-28T09:06:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
